--- a/data-request/dreq_default.xlsx
+++ b/data-request/dreq_default.xlsx
@@ -462,973 +462,973 @@
     <t>va200</t>
   </si>
   <si>
+    <t>va250</t>
+  </si>
+  <si>
+    <t>va300</t>
+  </si>
+  <si>
+    <t>va400</t>
+  </si>
+  <si>
+    <t>va500</t>
+  </si>
+  <si>
+    <t>va50m</t>
+  </si>
+  <si>
+    <t>va600</t>
+  </si>
+  <si>
+    <t>va700</t>
+  </si>
+  <si>
+    <t>va850</t>
+  </si>
+  <si>
+    <t>va925</t>
+  </si>
+  <si>
+    <t>wa1000</t>
+  </si>
+  <si>
+    <t>wa200</t>
+  </si>
+  <si>
+    <t>wa250</t>
+  </si>
+  <si>
+    <t>wa300</t>
+  </si>
+  <si>
+    <t>wa400</t>
+  </si>
+  <si>
+    <t>wa500</t>
+  </si>
+  <si>
+    <t>wa600</t>
+  </si>
+  <si>
+    <t>wa700</t>
+  </si>
+  <si>
+    <t>wa850</t>
+  </si>
+  <si>
+    <t>wa925</t>
+  </si>
+  <si>
+    <t>zg1000</t>
+  </si>
+  <si>
+    <t>zg200</t>
+  </si>
+  <si>
+    <t>zg250</t>
+  </si>
+  <si>
+    <t>zg300</t>
+  </si>
+  <si>
+    <t>zg400</t>
+  </si>
+  <si>
+    <t>zg500</t>
+  </si>
+  <si>
+    <t>zg600</t>
+  </si>
+  <si>
+    <t>zg700</t>
+  </si>
+  <si>
+    <t>zg850</t>
+  </si>
+  <si>
+    <t>zg925</t>
+  </si>
+  <si>
+    <t>zmla</t>
+  </si>
+  <si>
+    <t>atmosphere_mass_content_of_cloud_ice</t>
+  </si>
+  <si>
+    <t>atmosphere_mass_content_of_cloud_condensed_water</t>
+  </si>
+  <si>
+    <t>surface_upward_latent_heat_flux</t>
+  </si>
+  <si>
+    <t>surface_upward_sensible_heat_flux</t>
+  </si>
+  <si>
+    <t>soil_frozen_water_content</t>
+  </si>
+  <si>
+    <t>frozen_water_content_of_soil_layer</t>
+  </si>
+  <si>
+    <t>runoff_flux</t>
+  </si>
+  <si>
+    <t>surface_runoff_flux</t>
+  </si>
+  <si>
+    <t>mass_content_of_water_in_soil</t>
+  </si>
+  <si>
+    <t>mass_content_of_water_in_soil_layer</t>
+  </si>
+  <si>
+    <t>convective_precipitation_flux</t>
+  </si>
+  <si>
+    <t>snowfall_flux</t>
+  </si>
+  <si>
+    <t>atmosphere_mass_content_of_water_vapor</t>
+  </si>
+  <si>
+    <t>surface_upwelling_longwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>toa_outgoing_longwave_flux</t>
+  </si>
+  <si>
+    <t>surface_direct_downwelling_shortwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>toa_incoming_shortwave_flux</t>
+  </si>
+  <si>
+    <t>surface_upwelling_shortwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>toa_outgoing_shortwave_flux</t>
+  </si>
+  <si>
+    <t>sea_ice_area_fraction</t>
+  </si>
+  <si>
+    <t>surface_snow_area_fraction</t>
+  </si>
+  <si>
+    <t>surface_snow_thickness</t>
+  </si>
+  <si>
+    <t>surface_snow_melt_flux</t>
+  </si>
+  <si>
+    <t>surface_snow_amount</t>
+  </si>
+  <si>
+    <t>duration_of_sunshine</t>
+  </si>
+  <si>
+    <t>surface_downward_eastward_stress</t>
+  </si>
+  <si>
+    <t>surface_downward_northward_stress</t>
+  </si>
+  <si>
+    <t>surface_temperature</t>
+  </si>
+  <si>
+    <t>soil_temperature</t>
+  </si>
+  <si>
+    <t>upward_air_velocity</t>
+  </si>
+  <si>
+    <t>geopotential_height</t>
+  </si>
+  <si>
+    <t>atmosphere_boundary_layer_thickness</t>
+  </si>
+  <si>
+    <t>Ice Water Path</t>
+  </si>
+  <si>
+    <t>Condensed Water Path</t>
+  </si>
+  <si>
+    <t>Surface Upward Latent Heat Flux</t>
+  </si>
+  <si>
+    <t>Surface Upward Sensible Heat Flux</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 1000hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 200hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 250hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 300hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 400hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 500hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 50m</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 600hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 700hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 850hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 925hPa</t>
+  </si>
+  <si>
+    <t>Soil Frozen Water Content</t>
+  </si>
+  <si>
+    <t>Frozen Water Content in Upper Portion of Soil Column</t>
+  </si>
+  <si>
+    <t>Total Runoff</t>
+  </si>
+  <si>
+    <t>Surface Runoff</t>
+  </si>
+  <si>
+    <t>Frozen Water Content of Soil Layer</t>
+  </si>
+  <si>
+    <t>Total Soil Moisture Content</t>
+  </si>
+  <si>
+    <t>Total Water Content of Soil Layer</t>
+  </si>
+  <si>
+    <t>Moisture in Upper Portion of Soil Column</t>
+  </si>
+  <si>
+    <t>Convective Precipitation</t>
+  </si>
+  <si>
+    <t>Daily Maximum Hourly Precipitation Rate</t>
+  </si>
+  <si>
+    <t>Snowfall Flux</t>
+  </si>
+  <si>
+    <t>Water Vapor Path</t>
+  </si>
+  <si>
+    <t>Surface Upwelling Longwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Outgoing Longwave Radiation</t>
+  </si>
+  <si>
+    <t>Surface Direct Downwelling Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Incident Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>Surface Upwelling Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Outgoing Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>Daily Maximum Near-Surface Wind Speed</t>
+  </si>
+  <si>
+    <t>Sea-Ice Area Percentage (Atmospheric Grid)</t>
+  </si>
+  <si>
+    <t>Snow Area Percentage</t>
+  </si>
+  <si>
+    <t>Snow Depth</t>
+  </si>
+  <si>
+    <t>Surface Snow Melt</t>
+  </si>
+  <si>
+    <t>Surface Snow Amount</t>
+  </si>
+  <si>
+    <t>Daily Duration of Sunshine</t>
+  </si>
+  <si>
+    <t>Air Temperature at 1000hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 200hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 250hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 300hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 400hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 500hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 50m</t>
+  </si>
+  <si>
+    <t>Air Temperature at 600hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 700hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 850hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 925hPa</t>
+  </si>
+  <si>
+    <t>Surface Downward Eastward Wind Stress</t>
+  </si>
+  <si>
+    <t>Surface Downward Northward Wind Stress</t>
+  </si>
+  <si>
+    <t>Surface Temperature</t>
+  </si>
+  <si>
+    <t>Temperature of Soil</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 1000hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 100m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 150m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 200hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 250hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 300hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 400hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 500hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 50m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 600hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 700hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 850hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 925hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 1000hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 100m</t>
+  </si>
+  <si>
+    <t>Northward Wind at 150m</t>
+  </si>
+  <si>
+    <t>Northward Wind at 200hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 250hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 300hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 400hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 500hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 50m</t>
+  </si>
+  <si>
+    <t>Northward Wind at 600hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 700hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 850hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 925hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 1000hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 200hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 250hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 300hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 400hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 500hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 600hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 700hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 850hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 925hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 1000hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 200hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 250hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 300hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 400hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 500hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 600hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 700hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 850hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 925hPa</t>
+  </si>
+  <si>
+    <t>Height of Boundary Layer</t>
+  </si>
+  <si>
+    <t>kg m-2</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>area: mean where land time: mean</t>
+  </si>
+  <si>
+    <t>area: mean where land time: point</t>
+  </si>
+  <si>
+    <t>area: mean time: mean within hours time: maximum over hours</t>
+  </si>
+  <si>
+    <t>time: sum</t>
+  </si>
+  <si>
+    <t>time: sum within days time: mean over days</t>
+  </si>
+  <si>
+    <t>['6hr']</t>
+  </si>
+  <si>
+    <t>['mon', 'day', '6hr']</t>
+  </si>
+  <si>
+    <t>areacella</t>
+  </si>
+  <si>
+    <t>cape</t>
+  </si>
+  <si>
+    <t>capemax</t>
+  </si>
+  <si>
+    <t>cin</t>
+  </si>
+  <si>
+    <t>cinmax</t>
+  </si>
+  <si>
+    <t>clh</t>
+  </si>
+  <si>
+    <t>cll</t>
+  </si>
+  <si>
+    <t>clm</t>
+  </si>
+  <si>
+    <t>dtb</t>
+  </si>
+  <si>
+    <t>evspsblpot</t>
+  </si>
+  <si>
+    <t>hus10</t>
+  </si>
+  <si>
+    <t>hus100</t>
+  </si>
+  <si>
+    <t>hus150</t>
+  </si>
+  <si>
+    <t>hus20</t>
+  </si>
+  <si>
+    <t>hus30</t>
+  </si>
+  <si>
+    <t>hus50</t>
+  </si>
+  <si>
+    <t>hus70</t>
+  </si>
+  <si>
+    <t>li</t>
+  </si>
+  <si>
+    <t>limax</t>
+  </si>
+  <si>
+    <t>mrsofc</t>
+  </si>
+  <si>
+    <t>od550aer</t>
+  </si>
+  <si>
+    <t>rldscs</t>
+  </si>
+  <si>
+    <t>rluscs</t>
+  </si>
+  <si>
+    <t>rlutcs</t>
+  </si>
+  <si>
+    <t>rootd</t>
+  </si>
+  <si>
+    <t>rsdscs</t>
+  </si>
+  <si>
+    <t>rsuscs</t>
+  </si>
+  <si>
+    <t>rsutcs</t>
+  </si>
+  <si>
+    <t>sftgif</t>
+  </si>
+  <si>
+    <t>sftlaf</t>
+  </si>
+  <si>
+    <t>sfturf</t>
+  </si>
+  <si>
+    <t>ta10</t>
+  </si>
+  <si>
+    <t>ta100</t>
+  </si>
+  <si>
+    <t>ta150</t>
+  </si>
+  <si>
+    <t>ta20</t>
+  </si>
+  <si>
+    <t>ta30</t>
+  </si>
+  <si>
+    <t>ta50</t>
+  </si>
+  <si>
+    <t>ta70</t>
+  </si>
+  <si>
+    <t>ua10</t>
+  </si>
+  <si>
+    <t>ua100</t>
+  </si>
+  <si>
+    <t>ua150</t>
+  </si>
+  <si>
+    <t>ua20</t>
+  </si>
+  <si>
+    <t>ua200m</t>
+  </si>
+  <si>
+    <t>ua250m</t>
+  </si>
+  <si>
+    <t>ua30</t>
+  </si>
+  <si>
+    <t>ua300m</t>
+  </si>
+  <si>
+    <t>ua50</t>
+  </si>
+  <si>
+    <t>ua70</t>
+  </si>
+  <si>
+    <t>va10</t>
+  </si>
+  <si>
+    <t>va100</t>
+  </si>
+  <si>
+    <t>va150</t>
+  </si>
+  <si>
+    <t>va20</t>
+  </si>
+  <si>
     <t>va200m</t>
   </si>
   <si>
-    <t>va250</t>
-  </si>
-  <si>
     <t>va250m</t>
   </si>
   <si>
-    <t>va300</t>
+    <t>va30</t>
   </si>
   <si>
     <t>va300m</t>
   </si>
   <si>
-    <t>va400</t>
-  </si>
-  <si>
-    <t>va500</t>
-  </si>
-  <si>
-    <t>va50m</t>
-  </si>
-  <si>
-    <t>va600</t>
-  </si>
-  <si>
-    <t>va700</t>
-  </si>
-  <si>
-    <t>va850</t>
-  </si>
-  <si>
-    <t>va925</t>
-  </si>
-  <si>
-    <t>wa1000</t>
-  </si>
-  <si>
-    <t>wa200</t>
-  </si>
-  <si>
-    <t>wa250</t>
-  </si>
-  <si>
-    <t>wa300</t>
-  </si>
-  <si>
-    <t>wa400</t>
-  </si>
-  <si>
-    <t>wa500</t>
-  </si>
-  <si>
-    <t>wa600</t>
-  </si>
-  <si>
-    <t>wa700</t>
-  </si>
-  <si>
-    <t>wa850</t>
-  </si>
-  <si>
-    <t>wa925</t>
-  </si>
-  <si>
-    <t>zg1000</t>
-  </si>
-  <si>
-    <t>zg200</t>
-  </si>
-  <si>
-    <t>zg250</t>
-  </si>
-  <si>
-    <t>zg300</t>
-  </si>
-  <si>
-    <t>zg400</t>
-  </si>
-  <si>
-    <t>zg500</t>
-  </si>
-  <si>
-    <t>zg600</t>
-  </si>
-  <si>
-    <t>zg700</t>
-  </si>
-  <si>
-    <t>zg850</t>
-  </si>
-  <si>
-    <t>zg925</t>
-  </si>
-  <si>
-    <t>zmla</t>
-  </si>
-  <si>
-    <t>atmosphere_mass_content_of_cloud_ice</t>
-  </si>
-  <si>
-    <t>atmosphere_mass_content_of_cloud_condensed_water</t>
-  </si>
-  <si>
-    <t>surface_upward_latent_heat_flux</t>
-  </si>
-  <si>
-    <t>surface_upward_sensible_heat_flux</t>
-  </si>
-  <si>
-    <t>soil_frozen_water_content</t>
-  </si>
-  <si>
-    <t>frozen_water_content_of_soil_layer</t>
-  </si>
-  <si>
-    <t>runoff_flux</t>
-  </si>
-  <si>
-    <t>surface_runoff_flux</t>
-  </si>
-  <si>
-    <t>mass_content_of_water_in_soil</t>
-  </si>
-  <si>
-    <t>mass_content_of_water_in_soil_layer</t>
-  </si>
-  <si>
-    <t>convective_precipitation_flux</t>
-  </si>
-  <si>
-    <t>snowfall_flux</t>
-  </si>
-  <si>
-    <t>atmosphere_mass_content_of_water_vapor</t>
-  </si>
-  <si>
-    <t>surface_upwelling_longwave_flux_in_air</t>
-  </si>
-  <si>
-    <t>toa_outgoing_longwave_flux</t>
-  </si>
-  <si>
-    <t>surface_direct_downwelling_shortwave_flux_in_air</t>
-  </si>
-  <si>
-    <t>toa_incoming_shortwave_flux</t>
-  </si>
-  <si>
-    <t>surface_upwelling_shortwave_flux_in_air</t>
-  </si>
-  <si>
-    <t>toa_outgoing_shortwave_flux</t>
-  </si>
-  <si>
-    <t>sea_ice_area_fraction</t>
-  </si>
-  <si>
-    <t>surface_snow_area_fraction</t>
-  </si>
-  <si>
-    <t>surface_snow_thickness</t>
-  </si>
-  <si>
-    <t>surface_snow_melt_flux</t>
-  </si>
-  <si>
-    <t>surface_snow_amount</t>
-  </si>
-  <si>
-    <t>duration_of_sunshine</t>
-  </si>
-  <si>
-    <t>surface_downward_eastward_stress</t>
-  </si>
-  <si>
-    <t>surface_downward_northward_stress</t>
-  </si>
-  <si>
-    <t>surface_temperature</t>
-  </si>
-  <si>
-    <t>soil_temperature</t>
-  </si>
-  <si>
-    <t>upward_air_velocity</t>
-  </si>
-  <si>
-    <t>geopotential_height</t>
-  </si>
-  <si>
-    <t>atmosphere_boundary_layer_thickness</t>
-  </si>
-  <si>
-    <t>Ice Water Path</t>
-  </si>
-  <si>
-    <t>Condensed Water Path</t>
-  </si>
-  <si>
-    <t>Surface Upward Latent Heat Flux</t>
-  </si>
-  <si>
-    <t>Surface Upward Sensible Heat Flux</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 1000hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 200hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 250hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 300hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 400hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 500hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 50m</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 600hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 700hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 850hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 925hPa</t>
-  </si>
-  <si>
-    <t>Soil Frozen Water Content</t>
-  </si>
-  <si>
-    <t>Frozen Water Content in Upper Portion of Soil Column</t>
-  </si>
-  <si>
-    <t>Total Runoff</t>
-  </si>
-  <si>
-    <t>Surface Runoff</t>
-  </si>
-  <si>
-    <t>Frozen Water Content of Soil Layer</t>
-  </si>
-  <si>
-    <t>Total Soil Moisture Content</t>
-  </si>
-  <si>
-    <t>Total Water Content of Soil Layer</t>
-  </si>
-  <si>
-    <t>Moisture in Upper Portion of Soil Column</t>
-  </si>
-  <si>
-    <t>Convective Precipitation</t>
-  </si>
-  <si>
-    <t>Daily Maximum Hourly Precipitation Rate</t>
-  </si>
-  <si>
-    <t>Snowfall Flux</t>
-  </si>
-  <si>
-    <t>Water Vapor Path</t>
-  </si>
-  <si>
-    <t>Surface Upwelling Longwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Outgoing Longwave Radiation</t>
-  </si>
-  <si>
-    <t>Surface Direct Downwelling Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Incident Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>Surface Upwelling Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Outgoing Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>Daily Maximum Near-Surface Wind Speed</t>
-  </si>
-  <si>
-    <t>Sea-Ice Area Percentage (Atmospheric Grid)</t>
-  </si>
-  <si>
-    <t>Snow Area Percentage</t>
-  </si>
-  <si>
-    <t>Snow Depth</t>
-  </si>
-  <si>
-    <t>Surface Snow Melt</t>
-  </si>
-  <si>
-    <t>Surface Snow Amount</t>
-  </si>
-  <si>
-    <t>Daily Duration of Sunshine</t>
-  </si>
-  <si>
-    <t>Air Temperature at 1000hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 200hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 250hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 300hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 400hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 500hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 50m</t>
-  </si>
-  <si>
-    <t>Air Temperature at 600hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 700hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 850hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 925hPa</t>
-  </si>
-  <si>
-    <t>Surface Downward Eastward Wind Stress</t>
-  </si>
-  <si>
-    <t>Surface Downward Northward Wind Stress</t>
-  </si>
-  <si>
-    <t>Surface Temperature</t>
-  </si>
-  <si>
-    <t>Temperature of Soil</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 1000hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 100m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 150m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 200hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 250hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 300hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 400hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 500hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 50m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 600hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 700hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 850hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 925hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 1000hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 100m</t>
-  </si>
-  <si>
-    <t>Northward Wind at 150m</t>
-  </si>
-  <si>
-    <t>Northward Wind at 200hPa</t>
+    <t>va50</t>
+  </si>
+  <si>
+    <t>va70</t>
+  </si>
+  <si>
+    <t>wa10</t>
+  </si>
+  <si>
+    <t>wa100</t>
+  </si>
+  <si>
+    <t>wa150</t>
+  </si>
+  <si>
+    <t>wa20</t>
+  </si>
+  <si>
+    <t>wa30</t>
+  </si>
+  <si>
+    <t>wa50</t>
+  </si>
+  <si>
+    <t>wa70</t>
+  </si>
+  <si>
+    <t>wsgsmax</t>
+  </si>
+  <si>
+    <t>z0</t>
+  </si>
+  <si>
+    <t>zg10</t>
+  </si>
+  <si>
+    <t>zg100</t>
+  </si>
+  <si>
+    <t>zg150</t>
+  </si>
+  <si>
+    <t>zg20</t>
+  </si>
+  <si>
+    <t>zg30</t>
+  </si>
+  <si>
+    <t>zg50</t>
+  </si>
+  <si>
+    <t>zg70</t>
+  </si>
+  <si>
+    <t>cell_area</t>
+  </si>
+  <si>
+    <t>atmosphere_convective_available_potential_energy_wrt_surface</t>
+  </si>
+  <si>
+    <t>atmosphere_convective_inhibition_wrt_surface</t>
+  </si>
+  <si>
+    <t>cloud_area_fraction_in_atmosphere_layer</t>
+  </si>
+  <si>
+    <t>bedrock_depth_below_ground_level</t>
+  </si>
+  <si>
+    <t>water_potential_evaporation_flux</t>
+  </si>
+  <si>
+    <t>temperature_difference_between_ambient_air_and_air_lifted_adiabatically_from_the_surface</t>
+  </si>
+  <si>
+    <t>soil_moisture_content_at_field_capacity</t>
+  </si>
+  <si>
+    <t>atmosphere_optical_thickness_due_to_ambient_aerosol_particles</t>
+  </si>
+  <si>
+    <t>surface_downwelling_longwave_flux_in_air_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>surface_upwelling_longwave_flux_in_air_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>toa_outgoing_longwave_flux_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>root_depth</t>
+  </si>
+  <si>
+    <t>surface_downwelling_shortwave_flux_in_air_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>surface_upwelling_shortwave_flux_in_air_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>toa_outgoing_shortwave_flux_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>land_ice_area_fraction</t>
+  </si>
+  <si>
+    <t>area_fraction</t>
+  </si>
+  <si>
+    <t>wind_speed_of_gust</t>
+  </si>
+  <si>
+    <t>surface_roughness_length</t>
+  </si>
+  <si>
+    <t>Atmosphere Grid-Cell Area</t>
+  </si>
+  <si>
+    <t>Convective Available Potential Energy</t>
+  </si>
+  <si>
+    <t>Daily Maximum Convective Available Potential Energy</t>
+  </si>
+  <si>
+    <t>Convective Inhibition</t>
+  </si>
+  <si>
+    <t>Daily Maximum Convective Inhibition</t>
+  </si>
+  <si>
+    <t>High Level Cloud Fraction</t>
+  </si>
+  <si>
+    <t>Low Level Cloud Fraction</t>
+  </si>
+  <si>
+    <t>Mid Level Cloud Fraction</t>
+  </si>
+  <si>
+    <t>Depth to Bedrock</t>
+  </si>
+  <si>
+    <t>Potential Evapotranspiration</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 10hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 100hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 150hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 20hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 30hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 50hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 70hPa</t>
+  </si>
+  <si>
+    <t>Lifted Index</t>
+  </si>
+  <si>
+    <t>Daily Maximum Lifted Index</t>
+  </si>
+  <si>
+    <t>Capacity of Soil to Store Water  (Field Capacity)</t>
+  </si>
+  <si>
+    <t>Ambient Aerosol Optical Thickness at 550nm</t>
+  </si>
+  <si>
+    <t>Surface Downwelling Clear-Sky Longwave Radiation</t>
+  </si>
+  <si>
+    <t>Surface Upwelling Clear-Sky Longwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Outgoing Clear-Sky Longwave Radiation</t>
+  </si>
+  <si>
+    <t>Maximum Root Depth</t>
+  </si>
+  <si>
+    <t>Surface Downwelling Clear-Sky Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>Surface Upwelling Clear-Sky Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Outgoing Clear-Sky Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>Percentage of the Grid Cell Covered by Glacier</t>
+  </si>
+  <si>
+    <t>Percentage of the Grid Cell Occupied by Lake</t>
+  </si>
+  <si>
+    <t>Percentage of the Grid Cell Occupied by Urban Area</t>
+  </si>
+  <si>
+    <t>Air Temperature at 10hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 100hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 150hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 20hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 30hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 50hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 70hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 10hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 100hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 150hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 20hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 200m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 250m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 30hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 300m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 50hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 70hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 10hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 100hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 150hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 20hPa</t>
   </si>
   <si>
     <t>Northward Wind at 200m</t>
   </si>
   <si>
-    <t>Northward Wind at 250hPa</t>
-  </si>
-  <si>
     <t>Northward Wind at 250m</t>
   </si>
   <si>
-    <t>Northward Wind at 300hPa</t>
+    <t>Northward Wind at 30hPa</t>
   </si>
   <si>
     <t>Northward Wind at 300m</t>
-  </si>
-  <si>
-    <t>Northward Wind at 400hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 500hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 50m</t>
-  </si>
-  <si>
-    <t>Northward Wind at 600hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 700hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 850hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 925hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 1000hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 200hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 250hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 300hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 400hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 500hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 600hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 700hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 850hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 925hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 1000hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 200hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 250hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 300hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 400hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 500hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 600hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 700hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 850hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 925hPa</t>
-  </si>
-  <si>
-    <t>Height of Boundary Layer</t>
-  </si>
-  <si>
-    <t>kg m-2</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>area: mean where land time: mean</t>
-  </si>
-  <si>
-    <t>area: mean where land time: point</t>
-  </si>
-  <si>
-    <t>area: mean time: mean within hours time: maximum over hours</t>
-  </si>
-  <si>
-    <t>time: sum</t>
-  </si>
-  <si>
-    <t>time: sum within days time: mean over days</t>
-  </si>
-  <si>
-    <t>['6hr']</t>
-  </si>
-  <si>
-    <t>['mon', 'day', '6hr']</t>
-  </si>
-  <si>
-    <t>areacella</t>
-  </si>
-  <si>
-    <t>cape</t>
-  </si>
-  <si>
-    <t>capemax</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>cinmax</t>
-  </si>
-  <si>
-    <t>clh</t>
-  </si>
-  <si>
-    <t>cll</t>
-  </si>
-  <si>
-    <t>clm</t>
-  </si>
-  <si>
-    <t>dtb</t>
-  </si>
-  <si>
-    <t>evspsblpot</t>
-  </si>
-  <si>
-    <t>hus10</t>
-  </si>
-  <si>
-    <t>hus100</t>
-  </si>
-  <si>
-    <t>hus150</t>
-  </si>
-  <si>
-    <t>hus20</t>
-  </si>
-  <si>
-    <t>hus30</t>
-  </si>
-  <si>
-    <t>hus50</t>
-  </si>
-  <si>
-    <t>hus70</t>
-  </si>
-  <si>
-    <t>li</t>
-  </si>
-  <si>
-    <t>limax</t>
-  </si>
-  <si>
-    <t>mrsofc</t>
-  </si>
-  <si>
-    <t>od550aer</t>
-  </si>
-  <si>
-    <t>rldscs</t>
-  </si>
-  <si>
-    <t>rluscs</t>
-  </si>
-  <si>
-    <t>rlutcs</t>
-  </si>
-  <si>
-    <t>rootd</t>
-  </si>
-  <si>
-    <t>rsdscs</t>
-  </si>
-  <si>
-    <t>rsuscs</t>
-  </si>
-  <si>
-    <t>rsutcs</t>
-  </si>
-  <si>
-    <t>sftgif</t>
-  </si>
-  <si>
-    <t>sftlaf</t>
-  </si>
-  <si>
-    <t>sfturf</t>
-  </si>
-  <si>
-    <t>ta10</t>
-  </si>
-  <si>
-    <t>ta100</t>
-  </si>
-  <si>
-    <t>ta150</t>
-  </si>
-  <si>
-    <t>ta20</t>
-  </si>
-  <si>
-    <t>ta30</t>
-  </si>
-  <si>
-    <t>ta50</t>
-  </si>
-  <si>
-    <t>ta70</t>
-  </si>
-  <si>
-    <t>ua10</t>
-  </si>
-  <si>
-    <t>ua100</t>
-  </si>
-  <si>
-    <t>ua150</t>
-  </si>
-  <si>
-    <t>ua20</t>
-  </si>
-  <si>
-    <t>ua200m</t>
-  </si>
-  <si>
-    <t>ua250m</t>
-  </si>
-  <si>
-    <t>ua30</t>
-  </si>
-  <si>
-    <t>ua300m</t>
-  </si>
-  <si>
-    <t>ua50</t>
-  </si>
-  <si>
-    <t>ua70</t>
-  </si>
-  <si>
-    <t>va10</t>
-  </si>
-  <si>
-    <t>va100</t>
-  </si>
-  <si>
-    <t>va150</t>
-  </si>
-  <si>
-    <t>va20</t>
-  </si>
-  <si>
-    <t>va30</t>
-  </si>
-  <si>
-    <t>va50</t>
-  </si>
-  <si>
-    <t>va70</t>
-  </si>
-  <si>
-    <t>wa10</t>
-  </si>
-  <si>
-    <t>wa100</t>
-  </si>
-  <si>
-    <t>wa150</t>
-  </si>
-  <si>
-    <t>wa20</t>
-  </si>
-  <si>
-    <t>wa30</t>
-  </si>
-  <si>
-    <t>wa50</t>
-  </si>
-  <si>
-    <t>wa70</t>
-  </si>
-  <si>
-    <t>wsgsmax</t>
-  </si>
-  <si>
-    <t>z0</t>
-  </si>
-  <si>
-    <t>zg10</t>
-  </si>
-  <si>
-    <t>zg100</t>
-  </si>
-  <si>
-    <t>zg150</t>
-  </si>
-  <si>
-    <t>zg20</t>
-  </si>
-  <si>
-    <t>zg30</t>
-  </si>
-  <si>
-    <t>zg50</t>
-  </si>
-  <si>
-    <t>zg70</t>
-  </si>
-  <si>
-    <t>cell_area</t>
-  </si>
-  <si>
-    <t>atmosphere_convective_available_potential_energy_wrt_surface</t>
-  </si>
-  <si>
-    <t>atmosphere_convective_inhibition_wrt_surface</t>
-  </si>
-  <si>
-    <t>cloud_area_fraction_in_atmosphere_layer</t>
-  </si>
-  <si>
-    <t>bedrock_depth_below_ground_level</t>
-  </si>
-  <si>
-    <t>water_potential_evaporation_flux</t>
-  </si>
-  <si>
-    <t>temperature_difference_between_ambient_air_and_air_lifted_adiabatically_from_the_surface</t>
-  </si>
-  <si>
-    <t>soil_moisture_content_at_field_capacity</t>
-  </si>
-  <si>
-    <t>atmosphere_optical_thickness_due_to_ambient_aerosol_particles</t>
-  </si>
-  <si>
-    <t>surface_downwelling_longwave_flux_in_air_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>surface_upwelling_longwave_flux_in_air_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>toa_outgoing_longwave_flux_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>root_depth</t>
-  </si>
-  <si>
-    <t>surface_downwelling_shortwave_flux_in_air_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>surface_upwelling_shortwave_flux_in_air_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>toa_outgoing_shortwave_flux_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>land_ice_area_fraction</t>
-  </si>
-  <si>
-    <t>area_fraction</t>
-  </si>
-  <si>
-    <t>wind_speed_of_gust</t>
-  </si>
-  <si>
-    <t>surface_roughness_length</t>
-  </si>
-  <si>
-    <t>Atmosphere Grid-Cell Area</t>
-  </si>
-  <si>
-    <t>Convective Available Potential Energy</t>
-  </si>
-  <si>
-    <t>Daily Maximum Convective Available Potential Energy</t>
-  </si>
-  <si>
-    <t>Convective Inhibition</t>
-  </si>
-  <si>
-    <t>Daily Maximum Convective Inhibition</t>
-  </si>
-  <si>
-    <t>High Level Cloud Fraction</t>
-  </si>
-  <si>
-    <t>Low Level Cloud Fraction</t>
-  </si>
-  <si>
-    <t>Mid Level Cloud Fraction</t>
-  </si>
-  <si>
-    <t>Depth to Bedrock</t>
-  </si>
-  <si>
-    <t>Potential Evapotranspiration</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 10hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 100hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 150hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 20hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 30hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 50hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 70hPa</t>
-  </si>
-  <si>
-    <t>Lifted Index</t>
-  </si>
-  <si>
-    <t>Daily Maximum Lifted Index</t>
-  </si>
-  <si>
-    <t>Capacity of Soil to Store Water  (Field Capacity)</t>
-  </si>
-  <si>
-    <t>Ambient Aerosol Optical Thickness at 550nm</t>
-  </si>
-  <si>
-    <t>Surface Downwelling Clear-Sky Longwave Radiation</t>
-  </si>
-  <si>
-    <t>Surface Upwelling Clear-Sky Longwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Outgoing Clear-Sky Longwave Radiation</t>
-  </si>
-  <si>
-    <t>Maximum Root Depth</t>
-  </si>
-  <si>
-    <t>Surface Downwelling Clear-Sky Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>Surface Upwelling Clear-Sky Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Outgoing Clear-Sky Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>Percentage of the Grid Cell Covered by Glacier</t>
-  </si>
-  <si>
-    <t>Percentage of the Grid Cell Occupied by Lake</t>
-  </si>
-  <si>
-    <t>Percentage of the Grid Cell Occupied by Urban Area</t>
-  </si>
-  <si>
-    <t>Air Temperature at 10hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 100hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 150hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 20hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 30hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 50hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 70hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 10hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 100hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 150hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 20hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 200m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 250m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 30hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 300m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 50hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 70hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 10hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 100hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 150hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 20hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 30hPa</t>
   </si>
   <si>
     <t>Northward Wind at 50hPa</t>
@@ -2387,7 +2387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="40.7109375" customWidth="1"/>
@@ -2418,13 +2418,13 @@
         <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>64</v>
@@ -2450,13 +2450,13 @@
         <v>77</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>64</v>
@@ -2482,10 +2482,10 @@
         <v>78</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>60</v>
@@ -2502,10 +2502,10 @@
         <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>60</v>
@@ -2525,7 +2525,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>57</v>
@@ -2534,7 +2534,7 @@
         <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2557,7 +2557,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>57</v>
@@ -2566,7 +2566,7 @@
         <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2589,7 +2589,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>57</v>
@@ -2598,7 +2598,7 @@
         <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2621,7 +2621,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>57</v>
@@ -2630,7 +2630,7 @@
         <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2653,7 +2653,7 @@
         <v>26</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>57</v>
@@ -2662,7 +2662,7 @@
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2685,7 +2685,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>57</v>
@@ -2694,7 +2694,7 @@
         <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2717,7 +2717,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>57</v>
@@ -2749,7 +2749,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>57</v>
@@ -2758,7 +2758,7 @@
         <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2781,7 +2781,7 @@
         <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>57</v>
@@ -2790,7 +2790,7 @@
         <v>64</v>
       </c>
       <c r="F24" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2813,7 +2813,7 @@
         <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>57</v>
@@ -2822,7 +2822,7 @@
         <v>64</v>
       </c>
       <c r="F26" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2845,7 +2845,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>57</v>
@@ -2854,7 +2854,7 @@
         <v>64</v>
       </c>
       <c r="F28" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2874,16 +2874,16 @@
         <v>91</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F30" t="s">
         <v>72</v>
@@ -2895,10 +2895,10 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F31" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2906,16 +2906,16 @@
         <v>92</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F32" t="s">
         <v>72</v>
@@ -2927,7 +2927,7 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F33" t="s">
         <v>71</v>
@@ -2938,19 +2938,19 @@
         <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F34" t="s">
         <v>320</v>
-      </c>
-      <c r="F34" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2958,19 +2958,19 @@
         <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F35" t="s">
         <v>320</v>
-      </c>
-      <c r="F35" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2978,16 +2978,16 @@
         <v>95</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F36" t="s">
         <v>72</v>
@@ -2999,10 +2999,10 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F37" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -3010,16 +3010,16 @@
         <v>96</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F38" t="s">
         <v>72</v>
@@ -3031,10 +3031,10 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F39" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -3042,16 +3042,16 @@
         <v>97</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F40" t="s">
         <v>72</v>
@@ -3063,10 +3063,10 @@
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F41" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -3074,16 +3074,16 @@
         <v>98</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F42" t="s">
         <v>72</v>
@@ -3095,7 +3095,7 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F43" t="s">
         <v>71</v>
@@ -3106,10 +3106,10 @@
         <v>99</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>56</v>
@@ -3129,13 +3129,13 @@
         <v>28</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F45" t="s">
         <v>74</v>
@@ -3146,10 +3146,10 @@
         <v>101</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>56</v>
@@ -3166,13 +3166,13 @@
         <v>102</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>64</v>
@@ -3198,10 +3198,10 @@
         <v>103</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>60</v>
@@ -3218,10 +3218,10 @@
         <v>104</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>60</v>
@@ -3238,10 +3238,10 @@
         <v>105</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>60</v>
@@ -3258,10 +3258,10 @@
         <v>106</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>60</v>
@@ -3278,10 +3278,10 @@
         <v>107</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>60</v>
@@ -3298,10 +3298,10 @@
         <v>108</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>60</v>
@@ -3321,7 +3321,7 @@
         <v>33</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>61</v>
@@ -3350,10 +3350,10 @@
         <v>110</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>55</v>
@@ -3370,10 +3370,10 @@
         <v>111</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>55</v>
@@ -3382,7 +3382,7 @@
         <v>64</v>
       </c>
       <c r="F58" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -3402,16 +3402,16 @@
         <v>112</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F60" t="s">
         <v>72</v>
@@ -3423,10 +3423,10 @@
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F61" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -3434,19 +3434,19 @@
         <v>113</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F62" t="s">
         <v>320</v>
-      </c>
-      <c r="F62" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -3454,16 +3454,16 @@
         <v>114</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F63" t="s">
         <v>72</v>
@@ -3475,10 +3475,10 @@
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F64" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3486,16 +3486,16 @@
         <v>115</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F65" t="s">
         <v>74</v>
@@ -3507,7 +3507,7 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F66" t="s">
         <v>75</v>
@@ -3521,7 +3521,7 @@
         <v>35</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>62</v>
@@ -3530,7 +3530,7 @@
         <v>64</v>
       </c>
       <c r="F67" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -3553,7 +3553,7 @@
         <v>35</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>62</v>
@@ -3562,7 +3562,7 @@
         <v>64</v>
       </c>
       <c r="F69" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3585,7 +3585,7 @@
         <v>35</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>62</v>
@@ -3594,7 +3594,7 @@
         <v>64</v>
       </c>
       <c r="F71" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3617,7 +3617,7 @@
         <v>35</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>62</v>
@@ -3626,7 +3626,7 @@
         <v>64</v>
       </c>
       <c r="F73" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3649,7 +3649,7 @@
         <v>35</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>62</v>
@@ -3658,7 +3658,7 @@
         <v>64</v>
       </c>
       <c r="F75" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3681,7 +3681,7 @@
         <v>35</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>62</v>
@@ -3690,7 +3690,7 @@
         <v>64</v>
       </c>
       <c r="F77" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3713,7 +3713,7 @@
         <v>35</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>62</v>
@@ -3745,7 +3745,7 @@
         <v>35</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>62</v>
@@ -3754,7 +3754,7 @@
         <v>64</v>
       </c>
       <c r="F81" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3777,7 +3777,7 @@
         <v>35</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>62</v>
@@ -3786,7 +3786,7 @@
         <v>64</v>
       </c>
       <c r="F83" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3809,7 +3809,7 @@
         <v>35</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>62</v>
@@ -3818,7 +3818,7 @@
         <v>64</v>
       </c>
       <c r="F85" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3841,7 +3841,7 @@
         <v>35</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>62</v>
@@ -3850,7 +3850,7 @@
         <v>64</v>
       </c>
       <c r="F87" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3870,10 +3870,10 @@
         <v>127</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>59</v>
@@ -3890,10 +3890,10 @@
         <v>128</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>59</v>
@@ -3910,10 +3910,10 @@
         <v>129</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>62</v>
@@ -3942,16 +3942,16 @@
         <v>130</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F93" t="s">
         <v>72</v>
@@ -3963,10 +3963,10 @@
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F94" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3977,7 +3977,7 @@
         <v>36</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>61</v>
@@ -3986,7 +3986,7 @@
         <v>64</v>
       </c>
       <c r="F95" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -4009,7 +4009,7 @@
         <v>36</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>61</v>
@@ -4041,7 +4041,7 @@
         <v>36</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>61</v>
@@ -4073,7 +4073,7 @@
         <v>36</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>61</v>
@@ -4082,7 +4082,7 @@
         <v>64</v>
       </c>
       <c r="F101" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -4105,7 +4105,7 @@
         <v>36</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>61</v>
@@ -4114,7 +4114,7 @@
         <v>64</v>
       </c>
       <c r="F103" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -4137,7 +4137,7 @@
         <v>36</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>61</v>
@@ -4146,7 +4146,7 @@
         <v>64</v>
       </c>
       <c r="F105" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -4169,7 +4169,7 @@
         <v>36</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>61</v>
@@ -4178,7 +4178,7 @@
         <v>64</v>
       </c>
       <c r="F107" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -4201,7 +4201,7 @@
         <v>36</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>61</v>
@@ -4210,7 +4210,7 @@
         <v>64</v>
       </c>
       <c r="F109" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -4233,7 +4233,7 @@
         <v>36</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>61</v>
@@ -4265,7 +4265,7 @@
         <v>36</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>61</v>
@@ -4274,7 +4274,7 @@
         <v>64</v>
       </c>
       <c r="F113" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4297,7 +4297,7 @@
         <v>36</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>61</v>
@@ -4306,7 +4306,7 @@
         <v>64</v>
       </c>
       <c r="F115" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4329,7 +4329,7 @@
         <v>36</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>61</v>
@@ -4338,7 +4338,7 @@
         <v>64</v>
       </c>
       <c r="F117" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>61</v>
@@ -4370,7 +4370,7 @@
         <v>64</v>
       </c>
       <c r="F119" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4393,7 +4393,7 @@
         <v>37</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>61</v>
@@ -4402,7 +4402,7 @@
         <v>64</v>
       </c>
       <c r="F121" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4425,7 +4425,7 @@
         <v>37</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>61</v>
@@ -4457,7 +4457,7 @@
         <v>37</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>61</v>
@@ -4489,7 +4489,7 @@
         <v>37</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>61</v>
@@ -4498,7 +4498,7 @@
         <v>64</v>
       </c>
       <c r="F127" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4521,7 +4521,7 @@
         <v>37</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>61</v>
@@ -4530,7 +4530,7 @@
         <v>64</v>
       </c>
       <c r="F129" t="s">
-        <v>71</v>
+        <v>319</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4553,7 +4553,7 @@
         <v>37</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>61</v>
@@ -4562,7 +4562,7 @@
         <v>64</v>
       </c>
       <c r="F131" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4585,7 +4585,7 @@
         <v>37</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>61</v>
@@ -4594,7 +4594,7 @@
         <v>64</v>
       </c>
       <c r="F133" t="s">
-        <v>71</v>
+        <v>319</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4617,7 +4617,7 @@
         <v>37</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>61</v>
@@ -4626,7 +4626,7 @@
         <v>64</v>
       </c>
       <c r="F135" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4649,7 +4649,7 @@
         <v>37</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>61</v>
@@ -4681,7 +4681,7 @@
         <v>37</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>61</v>
@@ -4690,7 +4690,7 @@
         <v>64</v>
       </c>
       <c r="F139" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4713,7 +4713,7 @@
         <v>37</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>61</v>
@@ -4722,7 +4722,7 @@
         <v>64</v>
       </c>
       <c r="F141" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4745,7 +4745,7 @@
         <v>37</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>61</v>
@@ -4754,7 +4754,7 @@
         <v>64</v>
       </c>
       <c r="F143" t="s">
-        <v>71</v>
+        <v>319</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4777,7 +4777,7 @@
         <v>37</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>61</v>
@@ -4786,7 +4786,7 @@
         <v>64</v>
       </c>
       <c r="F145" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4806,10 +4806,10 @@
         <v>157</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>61</v>
@@ -4818,7 +4818,7 @@
         <v>64</v>
       </c>
       <c r="F147" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4838,10 +4838,10 @@
         <v>158</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>61</v>
@@ -4850,7 +4850,7 @@
         <v>64</v>
       </c>
       <c r="F149" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4870,10 +4870,10 @@
         <v>159</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>61</v>
@@ -4882,7 +4882,7 @@
         <v>64</v>
       </c>
       <c r="F151" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4902,10 +4902,10 @@
         <v>160</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>61</v>
@@ -4914,7 +4914,7 @@
         <v>64</v>
       </c>
       <c r="F153" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4934,10 +4934,10 @@
         <v>161</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>61</v>
@@ -4946,7 +4946,7 @@
         <v>64</v>
       </c>
       <c r="F155" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -4966,10 +4966,10 @@
         <v>162</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>61</v>
@@ -4978,7 +4978,7 @@
         <v>64</v>
       </c>
       <c r="F157" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4998,10 +4998,10 @@
         <v>163</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>61</v>
@@ -5010,7 +5010,7 @@
         <v>64</v>
       </c>
       <c r="F159" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -5030,10 +5030,10 @@
         <v>164</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>61</v>
@@ -5042,7 +5042,7 @@
         <v>64</v>
       </c>
       <c r="F161" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -5062,10 +5062,10 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>61</v>
@@ -5074,7 +5074,7 @@
         <v>64</v>
       </c>
       <c r="F163" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5094,10 +5094,10 @@
         <v>166</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>61</v>
@@ -5106,7 +5106,7 @@
         <v>64</v>
       </c>
       <c r="F165" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5126,19 +5126,19 @@
         <v>167</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F167" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5158,19 +5158,19 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F169" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -5190,19 +5190,19 @@
         <v>169</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F171" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -5222,10 +5222,10 @@
         <v>170</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>58</v>
@@ -5234,7 +5234,7 @@
         <v>64</v>
       </c>
       <c r="F173" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -5254,10 +5254,10 @@
         <v>171</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>58</v>
@@ -5266,7 +5266,7 @@
         <v>64</v>
       </c>
       <c r="F175" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -5286,10 +5286,10 @@
         <v>172</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>58</v>
@@ -5298,7 +5298,7 @@
         <v>64</v>
       </c>
       <c r="F177" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -5318,10 +5318,10 @@
         <v>173</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>58</v>
@@ -5330,7 +5330,7 @@
         <v>64</v>
       </c>
       <c r="F179" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -5350,10 +5350,10 @@
         <v>174</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>58</v>
@@ -5362,7 +5362,7 @@
         <v>64</v>
       </c>
       <c r="F181" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5382,10 +5382,10 @@
         <v>175</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>58</v>
@@ -5394,7 +5394,7 @@
         <v>64</v>
       </c>
       <c r="F183" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5414,10 +5414,10 @@
         <v>176</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>58</v>
@@ -5426,7 +5426,7 @@
         <v>64</v>
       </c>
       <c r="F185" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5446,10 +5446,10 @@
         <v>177</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>58</v>
@@ -5458,7 +5458,7 @@
         <v>64</v>
       </c>
       <c r="F187" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -5473,104 +5473,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
-      <c r="A189" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F189" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190" s="1"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
-      <c r="E190" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F190" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F191" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
-      <c r="E192" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F192" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F193" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194" s="1"/>
-      <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
-      <c r="E194" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F194" t="s">
-        <v>72</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="352">
+  <mergeCells count="340">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A8:A9"/>
@@ -5656,9 +5560,6 @@
     <mergeCell ref="A183:A184"/>
     <mergeCell ref="A185:A186"/>
     <mergeCell ref="A187:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A192"/>
-    <mergeCell ref="A193:A194"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B8:B9"/>
@@ -5744,9 +5645,6 @@
     <mergeCell ref="B183:B184"/>
     <mergeCell ref="B185:B186"/>
     <mergeCell ref="B187:B188"/>
-    <mergeCell ref="B189:B190"/>
-    <mergeCell ref="B191:B192"/>
-    <mergeCell ref="B193:B194"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C8:C9"/>
@@ -5832,9 +5730,6 @@
     <mergeCell ref="C183:C184"/>
     <mergeCell ref="C185:C186"/>
     <mergeCell ref="C187:C188"/>
-    <mergeCell ref="C189:C190"/>
-    <mergeCell ref="C191:C192"/>
-    <mergeCell ref="C193:C194"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="D8:D9"/>
@@ -5920,9 +5815,6 @@
     <mergeCell ref="D183:D184"/>
     <mergeCell ref="D185:D186"/>
     <mergeCell ref="D187:D188"/>
-    <mergeCell ref="D189:D190"/>
-    <mergeCell ref="D191:D192"/>
-    <mergeCell ref="D193:D194"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5930,7 +5822,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="40.7109375" customWidth="1"/>
@@ -5958,13 +5850,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>489</v>
@@ -5978,13 +5870,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>490</v>
@@ -6010,13 +5902,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>490</v>
@@ -6042,13 +5934,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>490</v>
@@ -6074,13 +5966,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>490</v>
@@ -6106,13 +5998,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>55</v>
@@ -6121,18 +6013,18 @@
         <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>55</v>
@@ -6141,18 +6033,18 @@
         <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>55</v>
@@ -6161,18 +6053,18 @@
         <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>58</v>
@@ -6186,19 +6078,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F15" t="s">
         <v>70</v>
@@ -6206,13 +6098,13 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>57</v>
@@ -6221,7 +6113,7 @@
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6238,13 +6130,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>57</v>
@@ -6253,7 +6145,7 @@
         <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -6270,13 +6162,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>57</v>
@@ -6285,7 +6177,7 @@
         <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -6302,13 +6194,13 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>57</v>
@@ -6317,7 +6209,7 @@
         <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -6334,13 +6226,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>57</v>
@@ -6349,7 +6241,7 @@
         <v>64</v>
       </c>
       <c r="F24" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -6366,13 +6258,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>57</v>
@@ -6381,7 +6273,7 @@
         <v>64</v>
       </c>
       <c r="F26" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -6398,13 +6290,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>57</v>
@@ -6413,7 +6305,7 @@
         <v>64</v>
       </c>
       <c r="F28" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -6430,13 +6322,13 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>62</v>
@@ -6462,13 +6354,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>62</v>
@@ -6494,16 +6386,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>492</v>
@@ -6514,13 +6406,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>57</v>
@@ -6534,13 +6426,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>60</v>
@@ -6549,18 +6441,18 @@
         <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>60</v>
@@ -6569,18 +6461,18 @@
         <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>60</v>
@@ -6589,18 +6481,18 @@
         <v>63</v>
       </c>
       <c r="F38" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>58</v>
@@ -6614,13 +6506,13 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>60</v>
@@ -6629,18 +6521,18 @@
         <v>63</v>
       </c>
       <c r="F40" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>60</v>
@@ -6649,18 +6541,18 @@
         <v>63</v>
       </c>
       <c r="F41" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>60</v>
@@ -6669,18 +6561,18 @@
         <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>55</v>
@@ -6694,13 +6586,13 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>55</v>
@@ -6714,13 +6606,13 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>55</v>
@@ -6734,13 +6626,13 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>62</v>
@@ -6749,7 +6641,7 @@
         <v>64</v>
       </c>
       <c r="F46" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -6766,13 +6658,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>62</v>
@@ -6781,7 +6673,7 @@
         <v>64</v>
       </c>
       <c r="F48" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -6798,13 +6690,13 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>62</v>
@@ -6813,7 +6705,7 @@
         <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -6830,13 +6722,13 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>62</v>
@@ -6845,7 +6737,7 @@
         <v>64</v>
       </c>
       <c r="F52" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -6862,13 +6754,13 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>62</v>
@@ -6877,7 +6769,7 @@
         <v>64</v>
       </c>
       <c r="F54" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -6894,13 +6786,13 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>62</v>
@@ -6909,7 +6801,7 @@
         <v>64</v>
       </c>
       <c r="F56" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -6926,13 +6818,13 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>62</v>
@@ -6941,7 +6833,7 @@
         <v>64</v>
       </c>
       <c r="F58" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -6958,13 +6850,13 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>61</v>
@@ -6973,7 +6865,7 @@
         <v>64</v>
       </c>
       <c r="F60" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -6990,13 +6882,13 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="1" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>61</v>
@@ -7005,7 +6897,7 @@
         <v>64</v>
       </c>
       <c r="F62" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -7022,13 +6914,13 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="1" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>61</v>
@@ -7037,7 +6929,7 @@
         <v>64</v>
       </c>
       <c r="F64" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -7054,13 +6946,13 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>61</v>
@@ -7069,7 +6961,7 @@
         <v>64</v>
       </c>
       <c r="F66" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -7086,13 +6978,13 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>61</v>
@@ -7118,13 +7010,13 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>61</v>
@@ -7150,13 +7042,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="1" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>61</v>
@@ -7165,7 +7057,7 @@
         <v>64</v>
       </c>
       <c r="F72" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -7182,13 +7074,13 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>61</v>
@@ -7214,13 +7106,13 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>61</v>
@@ -7229,7 +7121,7 @@
         <v>64</v>
       </c>
       <c r="F76" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -7246,13 +7138,13 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>61</v>
@@ -7261,7 +7153,7 @@
         <v>64</v>
       </c>
       <c r="F78" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -7278,13 +7170,13 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>61</v>
@@ -7293,7 +7185,7 @@
         <v>64</v>
       </c>
       <c r="F80" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -7310,13 +7202,13 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>61</v>
@@ -7325,7 +7217,7 @@
         <v>64</v>
       </c>
       <c r="F82" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -7342,13 +7234,13 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>61</v>
@@ -7357,7 +7249,7 @@
         <v>64</v>
       </c>
       <c r="F84" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -7374,13 +7266,13 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>61</v>
@@ -7389,7 +7281,7 @@
         <v>64</v>
       </c>
       <c r="F86" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -7406,13 +7298,13 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>61</v>
@@ -7421,7 +7313,7 @@
         <v>64</v>
       </c>
       <c r="F88" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -7438,13 +7330,13 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>61</v>
@@ -7453,7 +7345,7 @@
         <v>64</v>
       </c>
       <c r="F90" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -7470,13 +7362,13 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>61</v>
@@ -7485,7 +7377,7 @@
         <v>64</v>
       </c>
       <c r="F92" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -7502,13 +7394,13 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>61</v>
@@ -7517,7 +7409,7 @@
         <v>64</v>
       </c>
       <c r="F94" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -7534,13 +7426,13 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>61</v>
@@ -7549,7 +7441,7 @@
         <v>64</v>
       </c>
       <c r="F96" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -7566,13 +7458,13 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>61</v>
@@ -7581,7 +7473,7 @@
         <v>64</v>
       </c>
       <c r="F98" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -7598,13 +7490,13 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>61</v>
@@ -7613,7 +7505,7 @@
         <v>64</v>
       </c>
       <c r="F100" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -7630,13 +7522,13 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>61</v>
@@ -7645,7 +7537,7 @@
         <v>64</v>
       </c>
       <c r="F102" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -7662,13 +7554,13 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>61</v>
@@ -7677,7 +7569,7 @@
         <v>64</v>
       </c>
       <c r="F104" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -7694,13 +7586,13 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>61</v>
@@ -7709,7 +7601,7 @@
         <v>64</v>
       </c>
       <c r="F106" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -7726,22 +7618,22 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>416</v>
+        <v>207</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F108" t="s">
-        <v>74</v>
+        <v>319</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -7750,121 +7642,121 @@
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F109" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>417</v>
+        <v>207</v>
       </c>
       <c r="C110" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F110" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F111" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F112" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F113" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F114" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F115" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F110" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F111" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112" s="1"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F112" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F113" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F114" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F115" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116" s="1"/>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
       <c r="E116" s="1" t="s">
         <v>63</v>
       </c>
@@ -7874,13 +7766,13 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>58</v>
@@ -7889,7 +7781,7 @@
         <v>64</v>
       </c>
       <c r="F117" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -7906,13 +7798,13 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>58</v>
@@ -7921,7 +7813,7 @@
         <v>64</v>
       </c>
       <c r="F119" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -7938,13 +7830,13 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>58</v>
@@ -7953,7 +7845,7 @@
         <v>64</v>
       </c>
       <c r="F121" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -7970,13 +7862,13 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>58</v>
@@ -7985,7 +7877,7 @@
         <v>64</v>
       </c>
       <c r="F123" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -8000,8 +7892,104 @@
         <v>72</v>
       </c>
     </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F125" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F126" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F127" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F128" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F129" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F130" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="208">
+  <mergeCells count="220">
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
@@ -8047,13 +8035,16 @@
     <mergeCell ref="A104:A105"/>
     <mergeCell ref="A106:A107"/>
     <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
     <mergeCell ref="A117:A118"/>
     <mergeCell ref="A119:A120"/>
     <mergeCell ref="A121:A122"/>
     <mergeCell ref="A123:A124"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="A129:A130"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B8"/>
@@ -8099,13 +8090,16 @@
     <mergeCell ref="B104:B105"/>
     <mergeCell ref="B106:B107"/>
     <mergeCell ref="B108:B109"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B114:B115"/>
     <mergeCell ref="B117:B118"/>
     <mergeCell ref="B119:B120"/>
     <mergeCell ref="B121:B122"/>
     <mergeCell ref="B123:B124"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="B129:B130"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C7:C8"/>
@@ -8151,13 +8145,16 @@
     <mergeCell ref="C104:C105"/>
     <mergeCell ref="C106:C107"/>
     <mergeCell ref="C108:C109"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="C114:C115"/>
     <mergeCell ref="C117:C118"/>
     <mergeCell ref="C119:C120"/>
     <mergeCell ref="C121:C122"/>
     <mergeCell ref="C123:C124"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="C129:C130"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="D7:D8"/>
@@ -8203,13 +8200,16 @@
     <mergeCell ref="D104:D105"/>
     <mergeCell ref="D106:D107"/>
     <mergeCell ref="D108:D109"/>
-    <mergeCell ref="D111:D112"/>
-    <mergeCell ref="D113:D114"/>
-    <mergeCell ref="D115:D116"/>
+    <mergeCell ref="D110:D111"/>
+    <mergeCell ref="D112:D113"/>
+    <mergeCell ref="D114:D115"/>
     <mergeCell ref="D117:D118"/>
     <mergeCell ref="D119:D120"/>
     <mergeCell ref="D121:D122"/>
     <mergeCell ref="D123:D124"/>
+    <mergeCell ref="D125:D126"/>
+    <mergeCell ref="D127:D128"/>
+    <mergeCell ref="D129:D130"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
